--- a/proyecto_ev_colombia/data/raw/infraestructura_generacion_86_registros.xlsx
+++ b/proyecto_ev_colombia/data/raw/infraestructura_generacion_86_registros.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/jonatanstickcamposnunez/Developer/bootcamp/infoRocolectada/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{33251AC5-3FFC-1248-9E02-778F736889B8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8CCDE5F9-DEE2-0F49-90E9-3423C280A8B9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="600" windowWidth="67660" windowHeight="28200" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -453,7 +453,6 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <sheetPr filterMode="1"/>
   <dimension ref="A1:H87"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
@@ -518,7 +517,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="3" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A3">
         <v>2</v>
       </c>
@@ -544,7 +543,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="4" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A4">
         <v>3</v>
       </c>
@@ -570,7 +569,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="5" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A5">
         <v>4</v>
       </c>
@@ -596,7 +595,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="6" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A6">
         <v>5</v>
       </c>
@@ -622,7 +621,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="7" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A7">
         <v>6</v>
       </c>
@@ -648,7 +647,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="8" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A8">
         <v>7</v>
       </c>
@@ -674,7 +673,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="9" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A9">
         <v>8</v>
       </c>
@@ -700,7 +699,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="10" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A10">
         <v>9</v>
       </c>
@@ -726,7 +725,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="11" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A11">
         <v>10</v>
       </c>
@@ -752,7 +751,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="12" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A12">
         <v>11</v>
       </c>
@@ -804,7 +803,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="14" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A14">
         <v>13</v>
       </c>
@@ -830,7 +829,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="15" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A15">
         <v>14</v>
       </c>
@@ -856,7 +855,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="16" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A16">
         <v>15</v>
       </c>
@@ -882,7 +881,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="17" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A17">
         <v>16</v>
       </c>
@@ -908,7 +907,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="18" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A18">
         <v>17</v>
       </c>
@@ -934,7 +933,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="19" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A19">
         <v>18</v>
       </c>
@@ -960,7 +959,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="20" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A20">
         <v>19</v>
       </c>
@@ -986,7 +985,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="21" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A21">
         <v>20</v>
       </c>
@@ -1012,7 +1011,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="22" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A22">
         <v>21</v>
       </c>
@@ -1038,7 +1037,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="23" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A23">
         <v>22</v>
       </c>
@@ -1090,7 +1089,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="25" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A25">
         <v>24</v>
       </c>
@@ -1116,7 +1115,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="26" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A26">
         <v>25</v>
       </c>
@@ -1142,7 +1141,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="27" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A27">
         <v>26</v>
       </c>
@@ -1168,7 +1167,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="28" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A28">
         <v>27</v>
       </c>
@@ -1194,7 +1193,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="29" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A29">
         <v>28</v>
       </c>
@@ -1220,7 +1219,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="30" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A30">
         <v>29</v>
       </c>
@@ -1246,7 +1245,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="31" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A31">
         <v>30</v>
       </c>
@@ -1272,7 +1271,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="32" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A32">
         <v>31</v>
       </c>
@@ -1298,7 +1297,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="33" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A33">
         <v>32</v>
       </c>
@@ -1324,7 +1323,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="34" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A34">
         <v>33</v>
       </c>
@@ -1376,7 +1375,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="36" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A36">
         <v>35</v>
       </c>
@@ -1402,7 +1401,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="37" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A37">
         <v>36</v>
       </c>
@@ -1428,7 +1427,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="38" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A38">
         <v>37</v>
       </c>
@@ -1454,7 +1453,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="39" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A39">
         <v>38</v>
       </c>
@@ -1480,7 +1479,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="40" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A40">
         <v>39</v>
       </c>
@@ -1506,7 +1505,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="41" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+    <row r="41" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A41">
         <v>40</v>
       </c>
@@ -1532,7 +1531,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="42" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+    <row r="42" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A42">
         <v>41</v>
       </c>
@@ -1558,7 +1557,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="43" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+    <row r="43" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A43">
         <v>42</v>
       </c>
@@ -1584,7 +1583,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="44" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+    <row r="44" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A44">
         <v>43</v>
       </c>
@@ -1636,7 +1635,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="46" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+    <row r="46" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A46">
         <v>45</v>
       </c>
@@ -1662,7 +1661,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="47" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+    <row r="47" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A47">
         <v>46</v>
       </c>
@@ -1688,7 +1687,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="48" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+    <row r="48" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A48">
         <v>47</v>
       </c>
@@ -1714,7 +1713,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="49" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+    <row r="49" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A49">
         <v>48</v>
       </c>
@@ -1740,7 +1739,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="50" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+    <row r="50" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A50">
         <v>49</v>
       </c>
@@ -1766,7 +1765,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="51" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+    <row r="51" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A51">
         <v>50</v>
       </c>
@@ -1792,7 +1791,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="52" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+    <row r="52" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A52">
         <v>51</v>
       </c>
@@ -1818,7 +1817,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="53" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+    <row r="53" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A53">
         <v>52</v>
       </c>
@@ -1844,7 +1843,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="54" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+    <row r="54" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A54">
         <v>53</v>
       </c>
@@ -1870,7 +1869,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="55" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+    <row r="55" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A55">
         <v>54</v>
       </c>
@@ -1922,7 +1921,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="57" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+    <row r="57" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A57">
         <v>56</v>
       </c>
@@ -1948,7 +1947,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="58" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+    <row r="58" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A58">
         <v>57</v>
       </c>
@@ -1974,7 +1973,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="59" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+    <row r="59" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A59">
         <v>58</v>
       </c>
@@ -2000,7 +1999,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="60" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+    <row r="60" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A60">
         <v>59</v>
       </c>
@@ -2026,7 +2025,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="61" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+    <row r="61" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A61">
         <v>60</v>
       </c>
@@ -2052,7 +2051,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="62" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+    <row r="62" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A62">
         <v>61</v>
       </c>
@@ -2078,7 +2077,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="63" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+    <row r="63" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A63">
         <v>62</v>
       </c>
@@ -2104,7 +2103,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="64" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+    <row r="64" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A64">
         <v>63</v>
       </c>
@@ -2130,7 +2129,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="65" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+    <row r="65" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A65">
         <v>64</v>
       </c>
@@ -2156,7 +2155,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="66" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+    <row r="66" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A66">
         <v>65</v>
       </c>
@@ -2208,7 +2207,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="68" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+    <row r="68" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A68">
         <v>67</v>
       </c>
@@ -2234,7 +2233,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="69" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+    <row r="69" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A69">
         <v>68</v>
       </c>
@@ -2260,7 +2259,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="70" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+    <row r="70" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A70">
         <v>69</v>
       </c>
@@ -2286,7 +2285,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="71" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+    <row r="71" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A71">
         <v>70</v>
       </c>
@@ -2312,7 +2311,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="72" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+    <row r="72" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A72">
         <v>71</v>
       </c>
@@ -2338,7 +2337,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="73" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+    <row r="73" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A73">
         <v>72</v>
       </c>
@@ -2364,7 +2363,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="74" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+    <row r="74" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A74">
         <v>73</v>
       </c>
@@ -2390,7 +2389,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="75" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+    <row r="75" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A75">
         <v>74</v>
       </c>
@@ -2416,7 +2415,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="76" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+    <row r="76" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A76">
         <v>75</v>
       </c>
@@ -2442,7 +2441,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="77" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+    <row r="77" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A77">
         <v>76</v>
       </c>
@@ -2468,7 +2467,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="78" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+    <row r="78" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A78">
         <v>77</v>
       </c>
@@ -2494,7 +2493,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="79" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+    <row r="79" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A79">
         <v>78</v>
       </c>
@@ -2520,7 +2519,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="80" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+    <row r="80" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A80">
         <v>79</v>
       </c>
@@ -2546,7 +2545,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="81" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+    <row r="81" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A81">
         <v>80</v>
       </c>
@@ -2598,7 +2597,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="83" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+    <row r="83" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A83">
         <v>82</v>
       </c>
@@ -2624,7 +2623,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="84" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+    <row r="84" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A84">
         <v>83</v>
       </c>
@@ -2650,7 +2649,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="85" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+    <row r="85" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A85">
         <v>84</v>
       </c>
@@ -2676,7 +2675,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="86" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+    <row r="86" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A86">
         <v>85</v>
       </c>
@@ -2702,7 +2701,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="87" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+    <row r="87" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A87">
         <v>86</v>
       </c>
@@ -2729,13 +2728,7 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:H87" xr:uid="{00000000-0001-0000-0000-000000000000}">
-    <filterColumn colId="2">
-      <filters>
-        <filter val="Antioquia"/>
-      </filters>
-    </filterColumn>
-  </autoFilter>
+  <autoFilter ref="A1:H87" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>